--- a/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
   <si>
     <t>TC ID</t>
   </si>
@@ -176,7 +176,7 @@
     <t>Early Termination</t>
   </si>
   <si>
-    <t>20184</t>
+    <t>8956</t>
   </si>
   <si>
     <t>N/A</t>
@@ -185,13 +185,13 @@
     <t>Lost</t>
   </si>
   <si>
+    <t>30 Jul 2026</t>
+  </si>
+  <si>
     <t>21 May 2026</t>
   </si>
   <si>
-    <t>17 Mar 2026</t>
-  </si>
-  <si>
-    <t>REQ-757</t>
+    <t>REQ-854</t>
   </si>
   <si>
     <t>ORIX Motorpass</t>
@@ -206,40 +206,40 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Darryn</t>
-  </si>
-  <si>
-    <t>Grumley</t>
-  </si>
-  <si>
-    <t>29/04/1983</t>
-  </si>
-  <si>
-    <t>0494488844</t>
-  </si>
-  <si>
-    <t>darryn.j.grumley@exxonmobil.com.test</t>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Shakya</t>
+  </si>
+  <si>
+    <t>27 Jun 1986</t>
+  </si>
+  <si>
+    <t>333665987</t>
+  </si>
+  <si>
+    <t>sudeep.shakya@outlook.com.test</t>
   </si>
   <si>
     <t>Your Residential Address *</t>
   </si>
   <si>
-    <t>ESSO Australia Pty Ltd</t>
-  </si>
-  <si>
-    <t>DAZ734</t>
-  </si>
-  <si>
-    <t>MAZDA CX-60</t>
-  </si>
-  <si>
-    <t>30 Aug 2029</t>
+    <t>QBE Management Services Pty Ltd</t>
+  </si>
+  <si>
+    <t>FPJ50N</t>
+  </si>
+  <si>
+    <t>BYD DOLPHIN</t>
+  </si>
+  <si>
+    <t>13 Mar 2028</t>
   </si>
   <si>
     <t>C:\Automation\Test cases Novated App\Filestoupload\RemittanceAdvice.pdf</t>
   </si>
   <si>
-    <t>12 Jun 2026</t>
+    <t>1 Jul 2026</t>
   </si>
   <si>
     <t>TC002</t>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t>${TC001.Payout Valid-to Date}</t>
+  </si>
+  <si>
+    <t>Novated Finance</t>
+  </si>
+  <si>
+    <t>REQ-169</t>
+  </si>
+  <si>
+    <t>Notifications (0)</t>
+  </si>
+  <si>
+    <t>There are no Current quotes to display</t>
   </si>
 </sst>
 </file>
@@ -1343,34 +1355,34 @@
   <dimension ref="A1:AU10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.7" customWidth="1"/>
-    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.775" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.775" customWidth="1"/>
-    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="23.775" customWidth="1"/>
-    <col min="11" max="11" width="17.225" customWidth="1"/>
-    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="23" width="19.1083333333333" customWidth="1"/>
-    <col min="24" max="24" width="20.7" customWidth="1"/>
-    <col min="25" max="25" width="24.6" customWidth="1"/>
-    <col min="26" max="26" width="29.8" customWidth="1"/>
-    <col min="27" max="28" width="24.5" customWidth="1"/>
-    <col min="36" max="36" width="26.6" customWidth="1"/>
-    <col min="43" max="44" width="12.4" customWidth="1"/>
-    <col min="45" max="45" width="14.6" customWidth="1"/>
-    <col min="46" max="46" width="16.7" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
+    <col min="2" max="2" customWidth="true" width="20.7"/>
+    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
+    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
+    <col min="6" max="6" customWidth="true" width="16.775"/>
+    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
+    <col min="8" max="8" customWidth="true" width="21.775"/>
+    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
+    <col min="10" max="10" customWidth="true" width="23.775"/>
+    <col min="11" max="11" customWidth="true" width="17.225"/>
+    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
+    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
+    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
+    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
+    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
+    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
+    <col min="18" max="23" customWidth="true" width="19.1083333333333"/>
+    <col min="24" max="24" customWidth="true" width="20.7"/>
+    <col min="25" max="25" customWidth="true" width="24.6"/>
+    <col min="26" max="26" customWidth="true" width="29.8"/>
+    <col min="27" max="28" customWidth="true" width="24.5"/>
+    <col min="36" max="36" customWidth="true" width="26.6"/>
+    <col min="43" max="44" customWidth="true" width="12.4"/>
+    <col min="45" max="45" customWidth="true" width="14.6"/>
+    <col min="46" max="46" customWidth="true" width="16.7"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="69" spans="1:47">
+    <row r="1" s="1" customFormat="1" ht="41.4" spans="1:47">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1523,13 +1535,13 @@
       <c r="C2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>20185</v>
-      </c>
-      <c r="E2" s="6">
+        <v>8957.0</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>20185</v>
+        <v>8957.0</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1571,15 +1583,15 @@
         <v>53</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>20,185 km</v>
+        <v>8,957 km</v>
       </c>
       <c r="W2" s="7" t="str">
         <f>TEXT(C2,"#,##0")&amp;" km"</f>
-        <v>20,184 km</v>
+        <v>8,956 km</v>
       </c>
       <c r="X2" s="7" t="s">
         <v>55</v>
@@ -1605,7 +1617,7 @@
       </c>
       <c r="AF2" s="7" t="str">
         <f>_xlfn.CONCAT(AD2," ",AE2)</f>
-        <v>Darryn Grumley</v>
+        <v>Sudeep Shakya</v>
       </c>
       <c r="AG2" s="7" t="s">
         <v>61</v>
@@ -1624,13 +1636,13 @@
       </c>
       <c r="AL2" s="7" t="str">
         <f>AN2&amp;" - "&amp;AM2</f>
-        <v>MAZDA CX-60 - DAZ734</v>
+        <v>There are no Current quotes to display - Notifications (0)</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="AO2" s="7" t="s">
         <v>68</v>
@@ -1646,7 +1658,7 @@
       <c r="AT2" s="7"/>
       <c r="AU2" s="7"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:47">
+    <row r="3" s="2" customFormat="1" ht="55.2" spans="1:47">
       <c r="A3" s="4" t="s">
         <v>71</v>
       </c>
@@ -1773,7 +1785,9 @@
       <c r="AT3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="AU3" s="4"/>
+      <c r="AU3" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" spans="1:47">
       <c r="E5" s="8"/>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="112">
   <si>
     <t>TC ID</t>
   </si>
@@ -339,6 +339,32 @@
   </si>
   <si>
     <t>There are no Current quotes to display</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+86,510 km</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>SXBHG</t>
+  </si>
+  <si>
+    <t>WHKDOPZ</t>
+  </si>
+  <si>
+    <t>0412 345 678</t>
+  </si>
+  <si>
+    <t>10581@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>Komatsu Australia Pty Ltd</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+86,521 km</t>
   </si>
 </sst>
 </file>
@@ -1533,15 +1559,15 @@
         <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="D2" s="6" t="e">
         <f>C2+1</f>
-        <v>8957.0</v>
-      </c>
-      <c r="E2" s="6" t="n">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E2" s="6" t="e">
         <f>D2</f>
-        <v>8957.0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1585,13 +1611,13 @@
       <c r="U2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="V2" s="7" t="str">
+      <c r="V2" s="7" t="e">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>8,957 km</v>
-      </c>
-      <c r="W2" s="7" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W2" s="7" t="e">
         <f>TEXT(C2,"#,##0")&amp;" km"</f>
-        <v>8,956 km</v>
+        <v>#VALUE!</v>
       </c>
       <c r="X2" s="7" t="s">
         <v>55</v>
@@ -1607,32 +1633,32 @@
         <v>57</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="AF2" s="7" t="str">
         <f>_xlfn.CONCAT(AD2," ",AE2)</f>
-        <v>Sudeep Shakya</v>
+        <v>SXBHG WHKDOPZ</v>
       </c>
       <c r="AG2" s="7" t="s">
         <v>61</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="AJ2" s="7" t="s">
         <v>64</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AL2" s="7" t="str">
         <f>AN2&amp;" - "&amp;AM2</f>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/07_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="121">
   <si>
     <t>TC ID</t>
   </si>
@@ -365,6 +365,37 @@
   <si>
     <t>Latest Reading (kms)
 86,521 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+89,062 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+89,166 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,201 km</t>
+  </si>
+  <si>
+    <t>BTFWULH</t>
+  </si>
+  <si>
+    <t>ABDGO</t>
+  </si>
+  <si>
+    <t>0469 000 111</t>
+  </si>
+  <si>
+    <t>191799@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>AMP Capital Office and Industrial Pty Ltd</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,204 km</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1590,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D2" s="6" t="e">
         <f>C2+1</f>
@@ -1633,32 +1664,32 @@
         <v>57</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AF2" s="7" t="str">
         <f>_xlfn.CONCAT(AD2," ",AE2)</f>
-        <v>SXBHG WHKDOPZ</v>
+        <v>BTFWULH ABDGO</v>
       </c>
       <c r="AG2" s="7" t="s">
         <v>61</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="AJ2" s="7" t="s">
         <v>64</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AL2" s="7" t="str">
         <f>AN2&amp;" - "&amp;AM2</f>
